--- a/profiles/resume_data_alt.xlsx
+++ b/profiles/resume_data_alt.xlsx
@@ -24,13 +24,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +44,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -49,12 +52,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,52 +432,64 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Jill Doe</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>+1 (555) 987-6543</t>
+          <t>Jill Doe</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>jill.doe@email.com</t>
+          <t>+1 (555) 987-6543</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>jill.doe@email.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>linkedin</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>linkedin.com/in/jilldoe</t>
         </is>
@@ -482,11 +506,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Results-driven data scientist with expertise in machine learning and AI solutions. Passionate about transforming complex data into actionable insights that drive business growth. Proven track record of leading high-impact projects and building innovative analytics platforms.</t>
         </is>
@@ -503,88 +534,130 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Lead Data Scientist</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>DataCorp</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Seattle, WA</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Present</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Architected machine learning pipeline processing 10M+ daily transactions with 99.9% accuracy.</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Led cross-functional team of 6 engineers delivering predictive analytics platform ahead of schedule.</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Presented data-driven insights to C-suite executives influencing strategic business decisions.</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end_date</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>bullet_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>bullet_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>bullet_3</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Lead Data Scientist</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DataCorp</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Architected machine learning pipeline processing 10M+ daily transactions with 99.9% accuracy.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Led cross-functional team of 6 engineers delivering predictive analytics platform ahead of schedule.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Presented data-driven insights to C-suite executives influencing strategic business decisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Analytics Inc</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Built customer segmentation models increasing marketing ROI by 45%.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Designed automated reporting dashboards reducing manual analysis time by 70%.</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Collaborated with product teams to integrate analytics into customer-facing applications.</t>
         </is>
@@ -601,41 +674,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>institution</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>start_year</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end_year</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>detail_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detail_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Master of Science in Data Science</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Stanford University</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Stanford, CA</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Specialized in machine learning, statistical modeling, and big data analytics.</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Thesis: "Deep Learning Applications in Natural Language Processing for Healthcare"</t>
         </is>
@@ -652,28 +762,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Data Science &amp; ML</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Python, R, TensorFlow, PyTorch, scikit-learn, Pandas</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>skills</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Data Science &amp; ML</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Python, R, TensorFlow, PyTorch, scikit-learn, Pandas</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Tools &amp; Platforms</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>SQL, Spark, Airflow, Jupyter, Tableau, AWS SageMaker</t>
         </is>
@@ -690,21 +812,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>organization</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>dates</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Data Literacy Instructor</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Women in Tech Foundation</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>2020 -- Present</t>
         </is>
@@ -721,25 +860,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Trail Running</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>hobby</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Photography</t>
+          <t>Trail Running</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Cooking International Cuisine</t>
         </is>
@@ -756,28 +902,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>AWS Certified ML Specialist</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Amazon Web Services 2023</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>certificate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>details</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>AWS Certified ML Specialist</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Amazon Web Services 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>TensorFlow Developer Certificate</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Google - TensorFlow Developer Program 2022</t>
         </is>
